--- a/data/trans_camb/IP16A98-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16A98-Clase-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,7; 23,81</t>
+          <t>-11,36; 23,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 28,41</t>
+          <t>-5,01; 28,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,06; 27,09</t>
+          <t>-8,98; 27,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,81; 14,74</t>
+          <t>-14,05; 15,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 19,32</t>
+          <t>-6,0; 19,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 17,26</t>
+          <t>-6,37; 17,44</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>-96,73; 792,7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>-37,35; 921,33</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; 933,16</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-51,53; 916,23</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-98,53; —</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-47,43; 370,02</t>
+          <t>-49,03; 388,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-46,8; 386,76</t>
+          <t>-46,96; 406,69</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 33,53</t>
+          <t>-4,59; 34,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,19; 8,81</t>
+          <t>-14,02; 7,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-36,84; 8,75</t>
+          <t>-37,85; 10,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-39,85; 3,7</t>
+          <t>-39,96; 5,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,69; 15,79</t>
+          <t>-10,68; 16,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-18,06; 4,6</t>
+          <t>-16,63; 5,01</t>
         </is>
       </c>
     </row>
@@ -878,17 +878,17 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-93,76; 79,06</t>
+          <t>-93,07; 203,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-67,0; 320,51</t>
+          <t>-65,01; 341,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-88,08; 107,01</t>
+          <t>-84,1; 129,64</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-17,96; 40,52</t>
+          <t>-17,29; 37,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-23,18; 22,34</t>
+          <t>-23,64; 20,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-15,06; 34,52</t>
+          <t>-14,0; 36,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 48,22</t>
+          <t>-3,1; 47,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 28,48</t>
+          <t>-8,23; 27,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 30,83</t>
+          <t>-5,35; 31,99</t>
         </is>
       </c>
     </row>
@@ -1034,17 +1034,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-46,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-69,58; 649,85</t>
+          <t>-56,74; 726,36</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-47,47; 717,89</t>
+          <t>-44,66; 777,02</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 17,76</t>
+          <t>-6,69; 17,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-13,3; 24,04</t>
+          <t>-14,28; 23,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,22; 17,5</t>
+          <t>-9,56; 18,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 31,3</t>
+          <t>-6,22; 28,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 12,89</t>
+          <t>-4,88; 13,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,43; 17,73</t>
+          <t>-8,75; 18,61</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-41,99; 237,58</t>
+          <t>-41,21; 225,69</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-70,2; 250,15</t>
+          <t>-76,0; 274,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-47,4; 139,87</t>
+          <t>-41,79; 158,99</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-27,26; 302,66</t>
+          <t>-30,5; 232,88</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-29,6; 105,88</t>
+          <t>-25,59; 112,23</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-49,88; 132,35</t>
+          <t>-42,92; 146,08</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-11,53; 20,34</t>
+          <t>-10,6; 23,36</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,67; 25,52</t>
+          <t>-9,57; 24,02</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 27,47</t>
+          <t>-4,15; 31,39</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-14,85; 13,39</t>
+          <t>-15,12; 13,32</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 19,88</t>
+          <t>-4,54; 19,57</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 14,98</t>
+          <t>-7,46; 14,1</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-58,96; 321,33</t>
+          <t>-53,07; 430,31</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-44,31; 401,03</t>
+          <t>-45,82; 388,18</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-37,21; 526,19</t>
+          <t>-30,48; 644,3</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-72,34; 287,39</t>
+          <t>-72,61; 264,4</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-25,3; 240,25</t>
+          <t>-26,27; 205,98</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-35,87; 180,29</t>
+          <t>-40,56; 164,31</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-44,59; 9,93</t>
+          <t>-39,5; 11,53</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-14,47; 50,48</t>
+          <t>-12,5; 51,55</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-24,88; 32,34</t>
+          <t>-26,06; 30,94</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-19,52; 38,06</t>
+          <t>-17,38; 38,61</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-23,05; 15,72</t>
+          <t>-24,72; 15,03</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 34,74</t>
+          <t>-6,26; 34,83</t>
         </is>
       </c>
     </row>
@@ -1492,27 +1492,27 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-47,92; —</t>
+          <t>-41,76; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 586,15</t>
+          <t>-100,0; 472,91</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-69,25; 612,57</t>
+          <t>-60,51; 653,19</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-79,39; 219,71</t>
+          <t>-82,29; 168,78</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-29,41; 410,38</t>
+          <t>-23,41; 389,77</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 13,01</t>
+          <t>-2,36; 11,56</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 16,28</t>
+          <t>-3,08; 15,6</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 11,65</t>
+          <t>-3,53; 11,79</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 11,61</t>
+          <t>-4,78; 11,25</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 9,53</t>
+          <t>-0,61; 9,54</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 10,96</t>
+          <t>-1,8; 10,81</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-11,7; 145,84</t>
+          <t>-14,73; 126,16</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-22,51; 160,47</t>
+          <t>-22,66; 158,39</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-19,31; 92,11</t>
+          <t>-19,59; 95,31</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-23,28; 94,02</t>
+          <t>-25,07; 89,86</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 83,14</t>
+          <t>-4,91; 79,65</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 91,19</t>
+          <t>-11,08; 90,88</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A98-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16A98-Clase-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,36; 23,91</t>
+          <t>-10,65; 24,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 28,43</t>
+          <t>-3,64; 30,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 27,22</t>
+          <t>-9,3; 27,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,05; 15,45</t>
+          <t>-13,14; 15,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 19,16</t>
+          <t>-5,47; 19,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 17,44</t>
+          <t>-6,58; 16,52</t>
         </is>
       </c>
     </row>
@@ -707,17 +707,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-96,73; 792,7</t>
+          <t>-81,4; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-37,35; 921,33</t>
+          <t>-37,28; 1091,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 933,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -727,12 +727,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-49,03; 388,41</t>
+          <t>-50,41; 382,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-46,96; 406,69</t>
+          <t>-50,38; 376,61</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 34,15</t>
+          <t>-4,99; 32,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,02; 7,97</t>
+          <t>-13,02; 8,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-37,85; 10,89</t>
+          <t>-38,79; 9,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-39,96; 5,55</t>
+          <t>-42,47; 4,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,68; 16,83</t>
+          <t>-12,83; 14,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-16,63; 5,01</t>
+          <t>-17,47; 4,34</t>
         </is>
       </c>
     </row>
@@ -873,22 +873,22 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 258,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-93,07; 203,29</t>
+          <t>-93,33; 152,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-65,01; 341,31</t>
+          <t>-71,46; 241,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-84,1; 129,64</t>
+          <t>-84,35; 95,08</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-17,29; 37,77</t>
+          <t>-17,51; 37,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-23,64; 20,29</t>
+          <t>-24,96; 20,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,0; 36,91</t>
+          <t>-14,91; 35,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 47,12</t>
+          <t>-4,99; 44,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 27,19</t>
+          <t>-7,38; 28,08</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 31,99</t>
+          <t>-4,87; 30,95</t>
         </is>
       </c>
     </row>
@@ -1034,17 +1034,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-57,59; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-56,74; 726,36</t>
+          <t>-55,9; 699,01</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-44,66; 777,02</t>
+          <t>-42,09; 791,06</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 17,93</t>
+          <t>-7,21; 17,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-14,28; 23,39</t>
+          <t>-13,51; 24,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 18,1</t>
+          <t>-8,92; 20,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 28,46</t>
+          <t>-4,81; 29,74</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 13,2</t>
+          <t>-5,7; 14,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 18,61</t>
+          <t>-9,46; 18,55</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-41,21; 225,69</t>
+          <t>-39,11; 218,64</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-76,0; 274,52</t>
+          <t>-77,03; 271,31</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-41,79; 158,99</t>
+          <t>-42,01; 174,91</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-30,5; 232,88</t>
+          <t>-25,17; 231,12</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-25,59; 112,23</t>
+          <t>-30,6; 119,5</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-42,92; 146,08</t>
+          <t>-48,73; 138,71</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-10,6; 23,36</t>
+          <t>-11,06; 21,04</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-9,57; 24,02</t>
+          <t>-7,66; 25,87</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 31,39</t>
+          <t>-6,29; 29,82</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-15,12; 13,32</t>
+          <t>-14,73; 13,63</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 19,57</t>
+          <t>-5,3; 20,86</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 14,1</t>
+          <t>-7,83; 14,34</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-53,07; 430,31</t>
+          <t>-57,08; 297,3</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-45,82; 388,18</t>
+          <t>-42,75; 350,57</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-30,48; 644,3</t>
+          <t>-36,41; 630,48</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-72,61; 264,4</t>
+          <t>-71,97; 290,73</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-26,27; 205,98</t>
+          <t>-31,83; 257,8</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-40,56; 164,31</t>
+          <t>-41,82; 198,43</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-39,5; 11,53</t>
+          <t>-42,89; 13,8</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-12,5; 51,55</t>
+          <t>-13,1; 51,8</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-26,06; 30,94</t>
+          <t>-22,36; 34,83</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-17,38; 38,61</t>
+          <t>-16,19; 33,81</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-24,72; 15,03</t>
+          <t>-22,44; 14,14</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 34,83</t>
+          <t>-4,72; 36,3</t>
         </is>
       </c>
     </row>
@@ -1492,27 +1492,27 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-41,76; —</t>
+          <t>-41,29; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 472,91</t>
+          <t>-100,0; 540,66</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-60,51; 653,19</t>
+          <t>-67,16; 504,4</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-82,29; 168,78</t>
+          <t>-80,5; 146,65</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-23,41; 389,77</t>
+          <t>-23,24; 409,7</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 11,56</t>
+          <t>-1,88; 11,64</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 15,6</t>
+          <t>-3,28; 15,24</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 11,79</t>
+          <t>-5,24; 12,19</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 11,25</t>
+          <t>-4,86; 11,4</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 9,54</t>
+          <t>-0,85; 9,63</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 10,81</t>
+          <t>-1,7; 10,56</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-14,73; 126,16</t>
+          <t>-14,6; 126,39</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-22,66; 158,39</t>
+          <t>-24,56; 146,52</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-19,59; 95,31</t>
+          <t>-27,06; 94,24</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-25,07; 89,86</t>
+          <t>-24,96; 100,05</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 79,65</t>
+          <t>-7,05; 79,34</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-11,08; 90,88</t>
+          <t>-10,78; 85,31</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A98-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16A98-Clase-trans_camb.xlsx
@@ -513,19 +513,19 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido otros medicamentos</t>
+          <t>Menores que consumieron otros medicamentos</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6,92</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-0,39</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>5,63</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>12,76</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6,92</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,1</t>
+          <t>12,83</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,02</t>
+          <t>5,7</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,65; 24,24</t>
+          <t>-11,06; 27,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 30,99</t>
+          <t>-12,59; 16,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 27,2</t>
+          <t>-10,7; 23,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,14; 15,76</t>
+          <t>-5,29; 28,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 19,82</t>
+          <t>-5,02; 19,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 16,52</t>
+          <t>-5,03; 18,72</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>73,09%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-4,13%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>59,09%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>133,9%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>73,09%</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-11,58%</t>
+          <t>134,63%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>59,97%</t>
         </is>
       </c>
     </row>
@@ -707,12 +707,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-81,4; —</t>
+          <t>-98,53; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-37,28; 1091,89</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -722,17 +722,17 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-51,99; 931,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-50,41; 382,31</t>
+          <t>-47,43; 370,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-50,38; 376,61</t>
+          <t>-45,0; 414,26</t>
         </is>
       </c>
     </row>
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-11,66</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-14,97</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>10,69</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-1,25</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-11,66</t>
-        </is>
-      </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-14,27</t>
+          <t>-1,23</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-5,36</t>
+          <t>-5,72</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 32,85</t>
+          <t>-36,84; 8,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,02; 8,83</t>
+          <t>-41,03; 2,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-38,79; 9,3</t>
+          <t>-6,22; 33,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-42,47; 4,68</t>
+          <t>-13,15; 9,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-12,83; 14,8</t>
+          <t>-11,69; 15,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-17,47; 4,34</t>
+          <t>-18,37; 4,33</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-50,26%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-64,52%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>169,15%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-19,83%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-50,26%</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-61,5%</t>
+          <t>-19,46%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-43,39%</t>
+          <t>-46,23%</t>
         </is>
       </c>
     </row>
@@ -868,27 +868,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>-94,38; 74,51</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 258,05</t>
-        </is>
-      </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-93,33; 152,76</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-71,46; 241,49</t>
+          <t>-67,0; 320,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-84,35; 95,08</t>
+          <t>-89,12; 110,77</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>9,03</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>19,54</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>9,13</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-1,16</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>9,03</t>
-        </is>
-      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19,86</t>
+          <t>-1,23</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,18</t>
+          <t>11,36</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-17,51; 37,74</t>
+          <t>-15,06; 34,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-24,96; 20,5</t>
+          <t>-4,53; 47,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,91; 35,35</t>
+          <t>-17,96; 40,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 44,93</t>
+          <t>-22,57; 22,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 28,08</t>
+          <t>-8,35; 28,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 30,95</t>
+          <t>-7,11; 30,37</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>83,65%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>180,95%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>71,93%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-9,12%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>83,65%</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>183,95%</t>
+          <t>-9,71%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>104,51%</t>
+          <t>97,48%</t>
         </is>
       </c>
     </row>
@@ -1024,27 +1024,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>-55,44; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-57,59; —</t>
-        </is>
-      </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-55,9; 699,01</t>
+          <t>-69,58; 649,85</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-42,09; 791,06</t>
+          <t>-50,05; 645,5</t>
         </is>
       </c>
     </row>
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3,25</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>9,41</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>4,55</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>2,03</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>3,25</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7,95</t>
+          <t>3,78</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,99</t>
+          <t>6,81</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,21; 17,16</t>
+          <t>-10,22; 17,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-13,51; 24,93</t>
+          <t>-4,07; 35,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,92; 20,08</t>
+          <t>-7,41; 17,76</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 29,74</t>
+          <t>-8,37; 16,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 14,31</t>
+          <t>-5,36; 12,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,46; 18,55</t>
+          <t>-3,77; 20,05</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>17,84%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>51,58%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>33,34%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>14,89%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>17,84%</t>
-        </is>
-      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>42,27%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-39,11; 218,64</t>
+          <t>-47,4; 139,87</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-77,03; 271,31</t>
+          <t>-23,27; 341,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-42,01; 174,91</t>
+          <t>-41,99; 237,58</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-25,17; 231,12</t>
+          <t>-49,43; 214,49</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-30,6; 119,5</t>
+          <t>-29,6; 105,88</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-48,73; 138,71</t>
+          <t>-22,31; 167,1</t>
         </is>
       </c>
     </row>
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>11,66</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,2</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>4,3</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>8,17</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>11,66</t>
-        </is>
-      </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>0,16</t>
+          <t>7,14</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,58</t>
+          <t>3,16</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-11,06; 21,04</t>
+          <t>-6,54; 27,47</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,66; 25,87</t>
+          <t>-15,3; 12,9</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 29,82</t>
+          <t>-11,53; 20,34</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-14,73; 13,63</t>
+          <t>-9,22; 24,72</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 20,86</t>
+          <t>-4,44; 19,88</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 14,34</t>
+          <t>-7,14; 14,48</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>91,94%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-1,61%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>29,15%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>55,4%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>91,94%</t>
-        </is>
-      </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>22,97%</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-57,08; 297,3</t>
+          <t>-37,21; 526,19</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-42,75; 350,57</t>
+          <t>-74,15; 274,39</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-36,41; 630,48</t>
+          <t>-58,96; 321,33</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-71,97; 290,73</t>
+          <t>-46,19; 359,82</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-31,83; 257,8</t>
+          <t>-25,3; 240,25</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-41,82; 198,43</t>
+          <t>-37,66; 174,21</t>
         </is>
       </c>
     </row>
@@ -1373,22 +1373,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>3,42</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>5,3</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>-9,72</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>22,25</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>3,42</t>
-        </is>
-      </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8,3</t>
+          <t>22,16</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,44</t>
+          <t>13,14</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-42,89; 13,8</t>
+          <t>-24,88; 32,34</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-13,1; 51,8</t>
+          <t>-20,74; 33,58</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-22,36; 34,83</t>
+          <t>-44,59; 9,93</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-16,19; 33,81</t>
+          <t>-13,76; 50,65</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-22,44; 14,14</t>
+          <t>-23,05; 15,72</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 36,3</t>
+          <t>-7,65; 32,37</t>
         </is>
       </c>
     </row>
@@ -1449,22 +1449,22 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>17,62%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>27,29%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>-51,2%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>117,23%</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>17,62%</t>
-        </is>
-      </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>116,78%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>68,21%</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 586,15</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>-71,07; 499,2</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>-41,29; —</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 540,66</t>
-        </is>
-      </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-67,16; 504,4</t>
+          <t>-47,18; —</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-80,5; 146,65</t>
+          <t>-79,39; 219,71</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-23,24; 409,7</t>
+          <t>-30,48; 393,6</t>
         </is>
       </c>
     </row>
@@ -1529,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>3,9</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>2,85</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>4,89</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>5,65</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>3,9</t>
-        </is>
-      </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2,9</t>
+          <t>6,59</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,24</t>
+          <t>4,67</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 11,64</t>
+          <t>-3,54; 11,65</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 15,24</t>
+          <t>-4,37; 12,14</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 12,19</t>
+          <t>-1,7; 13,01</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 11,4</t>
+          <t>-1,0; 13,5</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 9,63</t>
+          <t>-1,0; 9,53</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 10,56</t>
+          <t>-0,18; 10,9</t>
         </is>
       </c>
     </row>
@@ -1605,22 +1605,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>24,71%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>18,07%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>39,79%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>45,95%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>24,71%</t>
-        </is>
-      </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>33,19%</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-14,6; 126,39</t>
+          <t>-19,31; 92,11</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-24,56; 146,52</t>
+          <t>-24,76; 99,34</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-27,06; 94,24</t>
+          <t>-11,7; 145,84</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-24,96; 100,05</t>
+          <t>-6,79; 159,91</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 79,34</t>
+          <t>-5,67; 83,14</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-10,78; 85,31</t>
+          <t>-1,36; 90,85</t>
         </is>
       </c>
     </row>
